--- a/data/医療圏人口動態R2-R7.xlsx
+++ b/data/医療圏人口動態R2-R7.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taro/WorksDownloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taro/works/dpc_dashboard/nagano_hospital_comparison/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{018858B1-6005-A544-BD1E-F0EBD0324DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19F9369-6A5C-D141-B6DB-11713A175E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{0638A67C-AA82-534F-8794-4B7521E1A603}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet9" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="37">
   <si>
     <t>コード</t>
   </si>
@@ -184,12 +184,15 @@
   <si>
     <t>R7</t>
   </si>
+  <si>
+    <t>R1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,6 +213,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Mincho Regular"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -269,7 +284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -324,6 +339,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -633,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94DF20D-8250-5443-B365-28EF6F1F4CE2}">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:9" ht="19">
@@ -675,23 +693,23 @@
       <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="8">
-        <v>362119</v>
-      </c>
-      <c r="F2" s="9">
-        <v>44885</v>
-      </c>
-      <c r="G2" s="9">
-        <v>206572</v>
-      </c>
-      <c r="H2" s="9">
-        <v>110662</v>
-      </c>
-      <c r="I2" s="9">
-        <v>60245</v>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="19">
+        <v>339171</v>
+      </c>
+      <c r="F2" s="19">
+        <v>38330</v>
+      </c>
+      <c r="G2" s="19">
+        <v>192504</v>
+      </c>
+      <c r="H2" s="19">
+        <v>108337</v>
+      </c>
+      <c r="I2" s="19">
+        <v>63930</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19">
@@ -704,23 +722,23 @@
       <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="8">
-        <v>49392</v>
-      </c>
-      <c r="F3" s="9">
-        <v>6092</v>
-      </c>
-      <c r="G3" s="9">
-        <v>27293</v>
-      </c>
-      <c r="H3" s="9">
-        <v>16007</v>
-      </c>
-      <c r="I3" s="9">
-        <v>8515</v>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="19">
+        <v>47828</v>
+      </c>
+      <c r="F3" s="19">
+        <v>5478</v>
+      </c>
+      <c r="G3" s="19">
+        <v>26358</v>
+      </c>
+      <c r="H3" s="19">
+        <v>15992</v>
+      </c>
+      <c r="I3" s="19">
+        <v>9645</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19">
@@ -733,23 +751,23 @@
       <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="8">
-        <v>42083</v>
-      </c>
-      <c r="F4" s="9">
-        <v>5227</v>
-      </c>
-      <c r="G4" s="9">
-        <v>23261</v>
-      </c>
-      <c r="H4" s="9">
-        <v>13595</v>
-      </c>
-      <c r="I4" s="9">
-        <v>7095</v>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="19">
+        <v>39842</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4418</v>
+      </c>
+      <c r="G4" s="19">
+        <v>21651</v>
+      </c>
+      <c r="H4" s="19">
+        <v>13773</v>
+      </c>
+      <c r="I4" s="19">
+        <v>7830</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="19">
@@ -762,23 +780,23 @@
       <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="8">
-        <v>19501</v>
-      </c>
-      <c r="F5" s="9">
-        <v>2021</v>
-      </c>
-      <c r="G5" s="9">
-        <v>9996</v>
-      </c>
-      <c r="H5" s="9">
-        <v>7484</v>
-      </c>
-      <c r="I5" s="9">
-        <v>4044</v>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="19">
+        <v>17706</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1639</v>
+      </c>
+      <c r="G5" s="19">
+        <v>8849</v>
+      </c>
+      <c r="H5" s="19">
+        <v>7218</v>
+      </c>
+      <c r="I5" s="19">
+        <v>4140</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="19">
@@ -791,23 +809,23 @@
       <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="8">
-        <v>58974</v>
-      </c>
-      <c r="F6" s="9">
-        <v>6966</v>
-      </c>
-      <c r="G6" s="9">
-        <v>32481</v>
-      </c>
-      <c r="H6" s="9">
-        <v>19527</v>
-      </c>
-      <c r="I6" s="9">
-        <v>10851</v>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="19">
+        <v>57008</v>
+      </c>
+      <c r="F6" s="19">
+        <v>6488</v>
+      </c>
+      <c r="G6" s="19">
+        <v>31032</v>
+      </c>
+      <c r="H6" s="19">
+        <v>19488</v>
+      </c>
+      <c r="I6" s="19">
+        <v>11812</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="19">
@@ -820,23 +838,23 @@
       <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="8">
-        <v>14168</v>
-      </c>
-      <c r="F7" s="9">
-        <v>1579</v>
-      </c>
-      <c r="G7" s="9">
-        <v>7537</v>
-      </c>
-      <c r="H7" s="9">
-        <v>5052</v>
-      </c>
-      <c r="I7" s="9">
-        <v>2784</v>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="19">
+        <v>12891</v>
+      </c>
+      <c r="F7" s="19">
+        <v>1219</v>
+      </c>
+      <c r="G7" s="19">
+        <v>6804</v>
+      </c>
+      <c r="H7" s="19">
+        <v>4868</v>
+      </c>
+      <c r="I7" s="19">
+        <v>3007</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19">
@@ -849,23 +867,23 @@
       <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="8">
-        <v>10486</v>
-      </c>
-      <c r="F8" s="9">
-        <v>1403</v>
-      </c>
-      <c r="G8" s="9">
-        <v>5403</v>
-      </c>
-      <c r="H8" s="9">
-        <v>3680</v>
-      </c>
-      <c r="I8" s="9">
-        <v>1920</v>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="19">
+        <v>10555</v>
+      </c>
+      <c r="F8" s="19">
+        <v>1360</v>
+      </c>
+      <c r="G8" s="19">
+        <v>5455</v>
+      </c>
+      <c r="H8" s="19">
+        <v>3740</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2310</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="19">
@@ -878,23 +896,23 @@
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="8">
-        <v>6613</v>
-      </c>
-      <c r="F9" s="9">
-        <v>736</v>
-      </c>
-      <c r="G9" s="9">
-        <v>3510</v>
-      </c>
-      <c r="H9" s="9">
-        <v>2367</v>
-      </c>
-      <c r="I9" s="9">
-        <v>1186</v>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="19">
+        <v>6125</v>
+      </c>
+      <c r="F9" s="19">
+        <v>549</v>
+      </c>
+      <c r="G9" s="19">
+        <v>3128</v>
+      </c>
+      <c r="H9" s="19">
+        <v>2448</v>
+      </c>
+      <c r="I9" s="19">
+        <v>1398</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19">
@@ -907,23 +925,23 @@
       <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8">
-        <v>11301</v>
-      </c>
-      <c r="F10" s="9">
-        <v>989</v>
-      </c>
-      <c r="G10" s="9">
-        <v>5551</v>
-      </c>
-      <c r="H10" s="9">
-        <v>4761</v>
-      </c>
-      <c r="I10" s="9">
-        <v>2675</v>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="19">
+        <v>10500</v>
+      </c>
+      <c r="F10" s="19">
+        <v>842</v>
+      </c>
+      <c r="G10" s="19">
+        <v>5116</v>
+      </c>
+      <c r="H10" s="19">
+        <v>4542</v>
+      </c>
+      <c r="I10" s="19">
+        <v>2725</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="19">
@@ -936,23 +954,23 @@
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="8">
-        <v>4331</v>
-      </c>
-      <c r="F11" s="9">
-        <v>495</v>
-      </c>
-      <c r="G11" s="9">
-        <v>2104</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1732</v>
-      </c>
-      <c r="I11" s="9">
-        <v>923</v>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="19">
+        <v>3910</v>
+      </c>
+      <c r="F11" s="19">
+        <v>399</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1817</v>
+      </c>
+      <c r="H11" s="19">
+        <v>1694</v>
+      </c>
+      <c r="I11" s="19">
+        <v>977</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="19">
@@ -965,23 +983,23 @@
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3367</v>
-      </c>
-      <c r="F12" s="9">
-        <v>369</v>
-      </c>
-      <c r="G12" s="9">
-        <v>1733</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1265</v>
-      </c>
-      <c r="I12" s="9">
-        <v>684</v>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="19">
+        <v>3216</v>
+      </c>
+      <c r="F12" s="19">
+        <v>311</v>
+      </c>
+      <c r="G12" s="19">
+        <v>1700</v>
+      </c>
+      <c r="H12" s="19">
+        <v>1205</v>
+      </c>
+      <c r="I12" s="19">
+        <v>690</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="19">
@@ -994,23 +1012,23 @@
       <c r="C13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="8">
-        <v>7596</v>
-      </c>
-      <c r="F13" s="9">
-        <v>655</v>
-      </c>
-      <c r="G13" s="9">
-        <v>3591</v>
-      </c>
-      <c r="H13" s="9">
-        <v>3350</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1709</v>
+      <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="19">
+        <v>7104</v>
+      </c>
+      <c r="F13" s="19">
+        <v>540</v>
+      </c>
+      <c r="G13" s="19">
+        <v>3309</v>
+      </c>
+      <c r="H13" s="19">
+        <v>3255</v>
+      </c>
+      <c r="I13" s="19">
+        <v>1859</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19">
@@ -1023,23 +1041,23 @@
       <c r="C14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2319</v>
-      </c>
-      <c r="F14" s="9">
-        <v>188</v>
-      </c>
-      <c r="G14" s="9">
-        <v>1026</v>
-      </c>
-      <c r="H14" s="9">
-        <v>1105</v>
-      </c>
-      <c r="I14" s="9">
-        <v>694</v>
+      <c r="D14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="19">
+        <v>2031</v>
+      </c>
+      <c r="F14" s="19">
+        <v>164</v>
+      </c>
+      <c r="G14" s="19">
+        <v>913</v>
+      </c>
+      <c r="H14" s="19">
+        <v>954</v>
+      </c>
+      <c r="I14" s="19">
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="19">
@@ -1052,23 +1070,23 @@
       <c r="C15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="8">
-        <v>10270</v>
-      </c>
-      <c r="F15" s="9">
-        <v>1031</v>
-      </c>
-      <c r="G15" s="9">
-        <v>5083</v>
-      </c>
-      <c r="H15" s="9">
-        <v>4156</v>
-      </c>
-      <c r="I15" s="9">
-        <v>2137</v>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="19">
+        <v>9634</v>
+      </c>
+      <c r="F15" s="19">
+        <v>954</v>
+      </c>
+      <c r="G15" s="19">
+        <v>4590</v>
+      </c>
+      <c r="H15" s="19">
+        <v>4090</v>
+      </c>
+      <c r="I15" s="19">
+        <v>2335</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="19">
@@ -1081,23 +1099,23 @@
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1665</v>
-      </c>
-      <c r="F16" s="9">
-        <v>108</v>
-      </c>
-      <c r="G16" s="9">
-        <v>661</v>
-      </c>
-      <c r="H16" s="9">
-        <v>896</v>
-      </c>
-      <c r="I16" s="9">
-        <v>555</v>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1438</v>
+      </c>
+      <c r="F16" s="19">
+        <v>97</v>
+      </c>
+      <c r="G16" s="19">
+        <v>521</v>
+      </c>
+      <c r="H16" s="19">
+        <v>820</v>
+      </c>
+      <c r="I16" s="19">
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="19">
@@ -1111,22 +1129,22 @@
         <v>10</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E17" s="8">
-        <v>350711</v>
-      </c>
-      <c r="F17" s="12">
-        <v>42317</v>
-      </c>
-      <c r="G17" s="12">
-        <v>199855</v>
-      </c>
-      <c r="H17" s="12">
-        <v>108539</v>
-      </c>
-      <c r="I17" s="12">
-        <v>58285</v>
+        <v>362119</v>
+      </c>
+      <c r="F17" s="9">
+        <v>44885</v>
+      </c>
+      <c r="G17" s="9">
+        <v>206572</v>
+      </c>
+      <c r="H17" s="9">
+        <v>110662</v>
+      </c>
+      <c r="I17" s="9">
+        <v>60245</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="19">
@@ -1140,22 +1158,22 @@
         <v>10</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E18" s="8">
-        <v>49122</v>
-      </c>
-      <c r="F18" s="12">
-        <v>5987</v>
-      </c>
-      <c r="G18" s="12">
-        <v>27048</v>
-      </c>
-      <c r="H18" s="12">
-        <v>16087</v>
-      </c>
-      <c r="I18" s="12">
-        <v>8514</v>
+        <v>49392</v>
+      </c>
+      <c r="F18" s="9">
+        <v>6092</v>
+      </c>
+      <c r="G18" s="9">
+        <v>27293</v>
+      </c>
+      <c r="H18" s="9">
+        <v>16007</v>
+      </c>
+      <c r="I18" s="9">
+        <v>8515</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="19">
@@ -1169,22 +1187,22 @@
         <v>15</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E19" s="8">
-        <v>41660</v>
-      </c>
-      <c r="F19" s="12">
-        <v>5020</v>
-      </c>
-      <c r="G19" s="12">
-        <v>22945</v>
-      </c>
-      <c r="H19" s="12">
-        <v>13695</v>
-      </c>
-      <c r="I19" s="12">
-        <v>7039</v>
+        <v>42083</v>
+      </c>
+      <c r="F19" s="9">
+        <v>5227</v>
+      </c>
+      <c r="G19" s="9">
+        <v>23261</v>
+      </c>
+      <c r="H19" s="9">
+        <v>13595</v>
+      </c>
+      <c r="I19" s="9">
+        <v>7095</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="19">
@@ -1198,22 +1216,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E20" s="8">
-        <v>19307</v>
-      </c>
-      <c r="F20" s="12">
-        <v>1955</v>
-      </c>
-      <c r="G20" s="12">
-        <v>9898</v>
-      </c>
-      <c r="H20" s="12">
-        <v>7454</v>
-      </c>
-      <c r="I20" s="12">
-        <v>3916</v>
+        <v>19501</v>
+      </c>
+      <c r="F20" s="9">
+        <v>2021</v>
+      </c>
+      <c r="G20" s="9">
+        <v>9996</v>
+      </c>
+      <c r="H20" s="9">
+        <v>7484</v>
+      </c>
+      <c r="I20" s="9">
+        <v>4044</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="19">
@@ -1227,22 +1245,22 @@
         <v>10</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E21" s="8">
-        <v>58376</v>
-      </c>
-      <c r="F21" s="12">
-        <v>6885</v>
-      </c>
-      <c r="G21" s="12">
-        <v>31816</v>
-      </c>
-      <c r="H21" s="12">
-        <v>19675</v>
-      </c>
-      <c r="I21" s="12">
-        <v>10842</v>
+        <v>58974</v>
+      </c>
+      <c r="F21" s="9">
+        <v>6966</v>
+      </c>
+      <c r="G21" s="9">
+        <v>32481</v>
+      </c>
+      <c r="H21" s="9">
+        <v>19527</v>
+      </c>
+      <c r="I21" s="9">
+        <v>10851</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="19">
@@ -1256,22 +1274,22 @@
         <v>10</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E22" s="8">
-        <v>13679</v>
-      </c>
-      <c r="F22" s="12">
-        <v>1467</v>
-      </c>
-      <c r="G22" s="12">
-        <v>7213</v>
-      </c>
-      <c r="H22" s="12">
-        <v>4999</v>
-      </c>
-      <c r="I22" s="12">
-        <v>2772</v>
+        <v>14168</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1579</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7537</v>
+      </c>
+      <c r="H22" s="9">
+        <v>5052</v>
+      </c>
+      <c r="I22" s="9">
+        <v>2784</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="19">
@@ -1285,22 +1303,22 @@
         <v>10</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E23" s="8">
-        <v>10649</v>
-      </c>
-      <c r="F23" s="12">
-        <v>1405</v>
-      </c>
-      <c r="G23" s="12">
-        <v>5494</v>
-      </c>
-      <c r="H23" s="12">
-        <v>3750</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1979</v>
+        <v>10486</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1403</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5403</v>
+      </c>
+      <c r="H23" s="9">
+        <v>3680</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1920</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="19">
@@ -1314,22 +1332,22 @@
         <v>10</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E24" s="8">
-        <v>6541</v>
-      </c>
-      <c r="F24" s="12">
-        <v>697</v>
-      </c>
-      <c r="G24" s="12">
-        <v>3402</v>
-      </c>
-      <c r="H24" s="12">
-        <v>2442</v>
-      </c>
-      <c r="I24" s="12">
-        <v>1224</v>
+        <v>6613</v>
+      </c>
+      <c r="F24" s="9">
+        <v>736</v>
+      </c>
+      <c r="G24" s="9">
+        <v>3510</v>
+      </c>
+      <c r="H24" s="9">
+        <v>2367</v>
+      </c>
+      <c r="I24" s="9">
+        <v>1186</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="19">
@@ -1343,22 +1361,22 @@
         <v>15</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E25" s="8">
-        <v>11188</v>
-      </c>
-      <c r="F25" s="12">
-        <v>958</v>
-      </c>
-      <c r="G25" s="12">
-        <v>5490</v>
-      </c>
-      <c r="H25" s="12">
-        <v>4740</v>
-      </c>
-      <c r="I25" s="12">
-        <v>2630</v>
+        <v>11301</v>
+      </c>
+      <c r="F25" s="9">
+        <v>989</v>
+      </c>
+      <c r="G25" s="9">
+        <v>5551</v>
+      </c>
+      <c r="H25" s="9">
+        <v>4761</v>
+      </c>
+      <c r="I25" s="9">
+        <v>2675</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="19">
@@ -1372,22 +1390,22 @@
         <v>15</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E26" s="8">
-        <v>4267</v>
-      </c>
-      <c r="F26" s="12">
-        <v>468</v>
-      </c>
-      <c r="G26" s="12">
-        <v>2042</v>
-      </c>
-      <c r="H26" s="12">
-        <v>1757</v>
-      </c>
-      <c r="I26" s="12">
-        <v>946</v>
+        <v>4331</v>
+      </c>
+      <c r="F26" s="9">
+        <v>495</v>
+      </c>
+      <c r="G26" s="9">
+        <v>2104</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1732</v>
+      </c>
+      <c r="I26" s="9">
+        <v>923</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="19">
@@ -1401,22 +1419,22 @@
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E27" s="8">
-        <v>3231</v>
-      </c>
-      <c r="F27" s="12">
-        <v>368</v>
-      </c>
-      <c r="G27" s="12">
-        <v>1608</v>
-      </c>
-      <c r="H27" s="12">
-        <v>1255</v>
-      </c>
-      <c r="I27" s="12">
-        <v>657</v>
+        <v>3367</v>
+      </c>
+      <c r="F27" s="9">
+        <v>369</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1733</v>
+      </c>
+      <c r="H27" s="9">
+        <v>1265</v>
+      </c>
+      <c r="I27" s="9">
+        <v>684</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="19">
@@ -1430,22 +1448,22 @@
         <v>10</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E28" s="8">
-        <v>7653</v>
-      </c>
-      <c r="F28" s="12">
-        <v>653</v>
-      </c>
-      <c r="G28" s="12">
-        <v>3580</v>
-      </c>
-      <c r="H28" s="12">
-        <v>3420</v>
-      </c>
-      <c r="I28" s="12">
-        <v>1711</v>
+        <v>7596</v>
+      </c>
+      <c r="F28" s="9">
+        <v>655</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3591</v>
+      </c>
+      <c r="H28" s="9">
+        <v>3350</v>
+      </c>
+      <c r="I28" s="9">
+        <v>1709</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="19">
@@ -1459,22 +1477,22 @@
         <v>10</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E29" s="8">
-        <v>2194</v>
-      </c>
-      <c r="F29" s="12">
-        <v>181</v>
-      </c>
-      <c r="G29" s="12">
-        <v>997</v>
-      </c>
-      <c r="H29" s="12">
-        <v>1016</v>
-      </c>
-      <c r="I29" s="12">
-        <v>601</v>
+        <v>2319</v>
+      </c>
+      <c r="F29" s="9">
+        <v>188</v>
+      </c>
+      <c r="G29" s="9">
+        <v>1026</v>
+      </c>
+      <c r="H29" s="9">
+        <v>1105</v>
+      </c>
+      <c r="I29" s="9">
+        <v>694</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="19">
@@ -1488,22 +1506,22 @@
         <v>10</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E30" s="8">
-        <v>10195</v>
-      </c>
-      <c r="F30" s="12">
-        <v>1010</v>
-      </c>
-      <c r="G30" s="12">
-        <v>5025</v>
-      </c>
-      <c r="H30" s="12">
-        <v>4160</v>
-      </c>
-      <c r="I30" s="12">
-        <v>2085</v>
+        <v>10270</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1031</v>
+      </c>
+      <c r="G30" s="9">
+        <v>5083</v>
+      </c>
+      <c r="H30" s="9">
+        <v>4156</v>
+      </c>
+      <c r="I30" s="9">
+        <v>2137</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="19">
@@ -1517,22 +1535,22 @@
         <v>15</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E31" s="8">
-        <v>1622</v>
-      </c>
-      <c r="F31" s="12">
-        <v>102</v>
-      </c>
-      <c r="G31" s="12">
-        <v>619</v>
-      </c>
-      <c r="H31" s="12">
-        <v>901</v>
-      </c>
-      <c r="I31" s="12">
-        <v>544</v>
+        <v>1665</v>
+      </c>
+      <c r="F31" s="9">
+        <v>108</v>
+      </c>
+      <c r="G31" s="9">
+        <v>661</v>
+      </c>
+      <c r="H31" s="9">
+        <v>896</v>
+      </c>
+      <c r="I31" s="9">
+        <v>555</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="19">
@@ -1546,22 +1564,22 @@
         <v>10</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="13">
-        <v>348283</v>
-      </c>
-      <c r="F32" s="14">
-        <v>41454</v>
-      </c>
-      <c r="G32" s="14">
-        <v>197823</v>
-      </c>
-      <c r="H32" s="15">
-        <v>109006</v>
-      </c>
-      <c r="I32" s="15">
-        <v>59149</v>
+        <v>28</v>
+      </c>
+      <c r="E32" s="8">
+        <v>350711</v>
+      </c>
+      <c r="F32" s="12">
+        <v>42317</v>
+      </c>
+      <c r="G32" s="12">
+        <v>199855</v>
+      </c>
+      <c r="H32" s="12">
+        <v>108539</v>
+      </c>
+      <c r="I32" s="12">
+        <v>58285</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="19">
@@ -1575,22 +1593,22 @@
         <v>10</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="13">
-        <v>48721</v>
-      </c>
-      <c r="F33" s="14">
-        <v>5850</v>
-      </c>
-      <c r="G33" s="14">
-        <v>26801</v>
-      </c>
-      <c r="H33" s="15">
-        <v>16070</v>
-      </c>
-      <c r="I33" s="15">
-        <v>8711</v>
+        <v>28</v>
+      </c>
+      <c r="E33" s="8">
+        <v>49122</v>
+      </c>
+      <c r="F33" s="12">
+        <v>5987</v>
+      </c>
+      <c r="G33" s="12">
+        <v>27048</v>
+      </c>
+      <c r="H33" s="12">
+        <v>16087</v>
+      </c>
+      <c r="I33" s="12">
+        <v>8514</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="19">
@@ -1604,22 +1622,22 @@
         <v>15</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="13">
-        <v>41144</v>
-      </c>
-      <c r="F34" s="14">
-        <v>4858</v>
-      </c>
-      <c r="G34" s="14">
-        <v>22545</v>
-      </c>
-      <c r="H34" s="15">
-        <v>13741</v>
-      </c>
-      <c r="I34" s="15">
-        <v>7159</v>
+        <v>28</v>
+      </c>
+      <c r="E34" s="8">
+        <v>41660</v>
+      </c>
+      <c r="F34" s="12">
+        <v>5020</v>
+      </c>
+      <c r="G34" s="12">
+        <v>22945</v>
+      </c>
+      <c r="H34" s="12">
+        <v>13695</v>
+      </c>
+      <c r="I34" s="12">
+        <v>7039</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="19">
@@ -1633,22 +1651,22 @@
         <v>15</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="13">
-        <v>19002</v>
-      </c>
-      <c r="F35" s="14">
-        <v>1901</v>
-      </c>
-      <c r="G35" s="14">
-        <v>9657</v>
-      </c>
-      <c r="H35" s="15">
-        <v>7444</v>
-      </c>
-      <c r="I35" s="15">
-        <v>3948</v>
+        <v>28</v>
+      </c>
+      <c r="E35" s="8">
+        <v>19307</v>
+      </c>
+      <c r="F35" s="12">
+        <v>1955</v>
+      </c>
+      <c r="G35" s="12">
+        <v>9898</v>
+      </c>
+      <c r="H35" s="12">
+        <v>7454</v>
+      </c>
+      <c r="I35" s="12">
+        <v>3916</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="19">
@@ -1662,22 +1680,22 @@
         <v>10</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="13">
-        <v>57964</v>
-      </c>
-      <c r="F36" s="14">
-        <v>6805</v>
-      </c>
-      <c r="G36" s="14">
-        <v>31446</v>
-      </c>
-      <c r="H36" s="15">
-        <v>19713</v>
-      </c>
-      <c r="I36" s="15">
-        <v>10983</v>
+        <v>28</v>
+      </c>
+      <c r="E36" s="8">
+        <v>58376</v>
+      </c>
+      <c r="F36" s="12">
+        <v>6885</v>
+      </c>
+      <c r="G36" s="12">
+        <v>31816</v>
+      </c>
+      <c r="H36" s="12">
+        <v>19675</v>
+      </c>
+      <c r="I36" s="12">
+        <v>10842</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="19">
@@ -1691,22 +1709,22 @@
         <v>10</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="13">
-        <v>13464</v>
-      </c>
-      <c r="F37" s="14">
-        <v>1407</v>
-      </c>
-      <c r="G37" s="14">
-        <v>7086</v>
-      </c>
-      <c r="H37" s="15">
-        <v>4971</v>
-      </c>
-      <c r="I37" s="15">
-        <v>2796</v>
+        <v>28</v>
+      </c>
+      <c r="E37" s="8">
+        <v>13679</v>
+      </c>
+      <c r="F37" s="12">
+        <v>1467</v>
+      </c>
+      <c r="G37" s="12">
+        <v>7213</v>
+      </c>
+      <c r="H37" s="12">
+        <v>4999</v>
+      </c>
+      <c r="I37" s="12">
+        <v>2772</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="19">
@@ -1720,22 +1738,22 @@
         <v>10</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="13">
-        <v>10623</v>
-      </c>
-      <c r="F38" s="14">
-        <v>1390</v>
-      </c>
-      <c r="G38" s="14">
-        <v>5465</v>
-      </c>
-      <c r="H38" s="15">
-        <v>3768</v>
-      </c>
-      <c r="I38" s="15">
-        <v>2031</v>
+        <v>28</v>
+      </c>
+      <c r="E38" s="8">
+        <v>10649</v>
+      </c>
+      <c r="F38" s="12">
+        <v>1405</v>
+      </c>
+      <c r="G38" s="12">
+        <v>5494</v>
+      </c>
+      <c r="H38" s="12">
+        <v>3750</v>
+      </c>
+      <c r="I38" s="12">
+        <v>1979</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="19">
@@ -1749,22 +1767,22 @@
         <v>10</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="13">
-        <v>6418</v>
-      </c>
-      <c r="F39" s="14">
-        <v>648</v>
-      </c>
-      <c r="G39" s="14">
-        <v>3331</v>
-      </c>
-      <c r="H39" s="15">
-        <v>2439</v>
-      </c>
-      <c r="I39" s="15">
-        <v>1250</v>
+        <v>28</v>
+      </c>
+      <c r="E39" s="8">
+        <v>6541</v>
+      </c>
+      <c r="F39" s="12">
+        <v>697</v>
+      </c>
+      <c r="G39" s="12">
+        <v>3402</v>
+      </c>
+      <c r="H39" s="12">
+        <v>2442</v>
+      </c>
+      <c r="I39" s="12">
+        <v>1224</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="19">
@@ -1778,22 +1796,22 @@
         <v>15</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="13">
-        <v>10899</v>
-      </c>
-      <c r="F40" s="14">
-        <v>922</v>
-      </c>
-      <c r="G40" s="14">
-        <v>5313</v>
-      </c>
-      <c r="H40" s="15">
-        <v>4664</v>
-      </c>
-      <c r="I40" s="15">
-        <v>2614</v>
+        <v>28</v>
+      </c>
+      <c r="E40" s="8">
+        <v>11188</v>
+      </c>
+      <c r="F40" s="12">
+        <v>958</v>
+      </c>
+      <c r="G40" s="12">
+        <v>5490</v>
+      </c>
+      <c r="H40" s="12">
+        <v>4740</v>
+      </c>
+      <c r="I40" s="12">
+        <v>2630</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="19">
@@ -1807,22 +1825,22 @@
         <v>15</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="13">
-        <v>4164</v>
-      </c>
-      <c r="F41" s="14">
-        <v>446</v>
-      </c>
-      <c r="G41" s="14">
-        <v>1999</v>
-      </c>
-      <c r="H41" s="15">
-        <v>1719</v>
-      </c>
-      <c r="I41" s="15">
-        <v>915</v>
+        <v>28</v>
+      </c>
+      <c r="E41" s="8">
+        <v>4267</v>
+      </c>
+      <c r="F41" s="12">
+        <v>468</v>
+      </c>
+      <c r="G41" s="12">
+        <v>2042</v>
+      </c>
+      <c r="H41" s="12">
+        <v>1757</v>
+      </c>
+      <c r="I41" s="12">
+        <v>946</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="19">
@@ -1836,22 +1854,22 @@
         <v>15</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="13">
-        <v>3169</v>
-      </c>
-      <c r="F42" s="14">
-        <v>352</v>
-      </c>
-      <c r="G42" s="14">
-        <v>1569</v>
-      </c>
-      <c r="H42" s="15">
-        <v>1248</v>
-      </c>
-      <c r="I42" s="15">
-        <v>648</v>
+        <v>28</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3231</v>
+      </c>
+      <c r="F42" s="12">
+        <v>368</v>
+      </c>
+      <c r="G42" s="12">
+        <v>1608</v>
+      </c>
+      <c r="H42" s="12">
+        <v>1255</v>
+      </c>
+      <c r="I42" s="12">
+        <v>657</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="19">
@@ -1865,22 +1883,22 @@
         <v>10</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" s="13">
-        <v>7514</v>
-      </c>
-      <c r="F43" s="14">
-        <v>615</v>
-      </c>
-      <c r="G43" s="14">
-        <v>3504</v>
-      </c>
-      <c r="H43" s="15">
-        <v>3395</v>
-      </c>
-      <c r="I43" s="15">
-        <v>1734</v>
+        <v>28</v>
+      </c>
+      <c r="E43" s="8">
+        <v>7653</v>
+      </c>
+      <c r="F43" s="12">
+        <v>653</v>
+      </c>
+      <c r="G43" s="12">
+        <v>3580</v>
+      </c>
+      <c r="H43" s="12">
+        <v>3420</v>
+      </c>
+      <c r="I43" s="12">
+        <v>1711</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="19">
@@ -1894,22 +1912,22 @@
         <v>10</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="13">
-        <v>2188</v>
-      </c>
-      <c r="F44" s="14">
-        <v>178</v>
-      </c>
-      <c r="G44" s="14">
-        <v>996</v>
-      </c>
-      <c r="H44" s="15">
-        <v>1014</v>
-      </c>
-      <c r="I44" s="15">
-        <v>599</v>
+        <v>28</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2194</v>
+      </c>
+      <c r="F44" s="12">
+        <v>181</v>
+      </c>
+      <c r="G44" s="12">
+        <v>997</v>
+      </c>
+      <c r="H44" s="12">
+        <v>1016</v>
+      </c>
+      <c r="I44" s="12">
+        <v>601</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="19">
@@ -1917,28 +1935,28 @@
         <v>588</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="13">
-        <v>10073</v>
-      </c>
-      <c r="F45" s="14">
-        <v>1015</v>
-      </c>
-      <c r="G45" s="14">
-        <v>4905</v>
-      </c>
-      <c r="H45" s="15">
-        <v>4153</v>
-      </c>
-      <c r="I45" s="15">
-        <v>2134</v>
+        <v>28</v>
+      </c>
+      <c r="E45" s="8">
+        <v>10195</v>
+      </c>
+      <c r="F45" s="12">
+        <v>1010</v>
+      </c>
+      <c r="G45" s="12">
+        <v>5025</v>
+      </c>
+      <c r="H45" s="12">
+        <v>4160</v>
+      </c>
+      <c r="I45" s="12">
+        <v>2085</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="19">
@@ -1952,457 +1970,457 @@
         <v>15</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="13">
-        <v>1571</v>
-      </c>
-      <c r="F46" s="14">
-        <v>93</v>
-      </c>
-      <c r="G46" s="14">
-        <v>588</v>
-      </c>
-      <c r="H46" s="15">
-        <v>890</v>
-      </c>
-      <c r="I46" s="15">
-        <v>536</v>
+        <v>28</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1622</v>
+      </c>
+      <c r="F46" s="12">
+        <v>102</v>
+      </c>
+      <c r="G46" s="12">
+        <v>619</v>
+      </c>
+      <c r="H46" s="12">
+        <v>901</v>
+      </c>
+      <c r="I46" s="12">
+        <v>544</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="19">
       <c r="A47" s="6">
         <v>201</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="17">
-        <v>345222</v>
-      </c>
-      <c r="F47" s="17">
-        <v>40467</v>
-      </c>
-      <c r="G47" s="17">
-        <v>196078</v>
-      </c>
-      <c r="H47" s="17">
-        <v>108677</v>
-      </c>
-      <c r="I47" s="17">
-        <v>60963</v>
+      <c r="C47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="13">
+        <v>348283</v>
+      </c>
+      <c r="F47" s="14">
+        <v>41454</v>
+      </c>
+      <c r="G47" s="14">
+        <v>197823</v>
+      </c>
+      <c r="H47" s="15">
+        <v>109006</v>
+      </c>
+      <c r="I47" s="15">
+        <v>59149</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="19">
       <c r="A48" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" s="17">
-        <v>48528</v>
-      </c>
-      <c r="F48" s="17">
-        <v>5746</v>
-      </c>
-      <c r="G48" s="17">
-        <v>26845</v>
-      </c>
-      <c r="H48" s="17">
-        <v>15937</v>
-      </c>
-      <c r="I48" s="17">
-        <v>8998</v>
+      <c r="C48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="13">
+        <v>48721</v>
+      </c>
+      <c r="F48" s="14">
+        <v>5850</v>
+      </c>
+      <c r="G48" s="14">
+        <v>26801</v>
+      </c>
+      <c r="H48" s="15">
+        <v>16070</v>
+      </c>
+      <c r="I48" s="15">
+        <v>8711</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="19">
       <c r="A49" s="10">
         <v>211</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="17">
-        <v>40702</v>
-      </c>
-      <c r="F49" s="17">
-        <v>4740</v>
-      </c>
-      <c r="G49" s="17">
-        <v>22208</v>
-      </c>
-      <c r="H49" s="17">
-        <v>13754</v>
-      </c>
-      <c r="I49" s="17">
-        <v>7385</v>
+      <c r="D49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="13">
+        <v>41144</v>
+      </c>
+      <c r="F49" s="14">
+        <v>4858</v>
+      </c>
+      <c r="G49" s="14">
+        <v>22545</v>
+      </c>
+      <c r="H49" s="15">
+        <v>13741</v>
+      </c>
+      <c r="I49" s="15">
+        <v>7159</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="19">
       <c r="A50" s="10">
         <v>213</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" s="17">
-        <v>18536</v>
-      </c>
-      <c r="F50" s="17">
-        <v>1796</v>
-      </c>
-      <c r="G50" s="17">
-        <v>9400</v>
-      </c>
-      <c r="H50" s="17">
-        <v>7340</v>
-      </c>
-      <c r="I50" s="17">
-        <v>3979</v>
+      <c r="D50" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="13">
+        <v>19002</v>
+      </c>
+      <c r="F50" s="14">
+        <v>1901</v>
+      </c>
+      <c r="G50" s="14">
+        <v>9657</v>
+      </c>
+      <c r="H50" s="15">
+        <v>7444</v>
+      </c>
+      <c r="I50" s="15">
+        <v>3948</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="19">
       <c r="A51" s="6">
         <v>218</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="17">
-        <v>57774</v>
-      </c>
-      <c r="F51" s="17">
-        <v>6767</v>
-      </c>
-      <c r="G51" s="17">
-        <v>31409</v>
-      </c>
-      <c r="H51" s="17">
-        <v>19598</v>
-      </c>
-      <c r="I51" s="17">
-        <v>11280</v>
+      <c r="B51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="13">
+        <v>57964</v>
+      </c>
+      <c r="F51" s="14">
+        <v>6805</v>
+      </c>
+      <c r="G51" s="14">
+        <v>31446</v>
+      </c>
+      <c r="H51" s="15">
+        <v>19713</v>
+      </c>
+      <c r="I51" s="15">
+        <v>10983</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="19">
       <c r="A52" s="6">
         <v>521</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="17">
-        <v>13344</v>
-      </c>
-      <c r="F52" s="17">
-        <v>1317</v>
-      </c>
-      <c r="G52" s="17">
-        <v>7099</v>
-      </c>
-      <c r="H52" s="17">
-        <v>4928</v>
-      </c>
-      <c r="I52" s="17">
-        <v>2883</v>
+      <c r="C52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="13">
+        <v>13464</v>
+      </c>
+      <c r="F52" s="14">
+        <v>1407</v>
+      </c>
+      <c r="G52" s="14">
+        <v>7086</v>
+      </c>
+      <c r="H52" s="15">
+        <v>4971</v>
+      </c>
+      <c r="I52" s="15">
+        <v>2796</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="19">
       <c r="A53" s="6">
         <v>541</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" s="17">
-        <v>10634</v>
-      </c>
-      <c r="F53" s="17">
-        <v>1400</v>
-      </c>
-      <c r="G53" s="17">
-        <v>5493</v>
-      </c>
-      <c r="H53" s="17">
-        <v>3741</v>
-      </c>
-      <c r="I53" s="17">
-        <v>2119</v>
+      <c r="C53" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="13">
+        <v>10623</v>
+      </c>
+      <c r="F53" s="14">
+        <v>1390</v>
+      </c>
+      <c r="G53" s="14">
+        <v>5465</v>
+      </c>
+      <c r="H53" s="15">
+        <v>3768</v>
+      </c>
+      <c r="I53" s="15">
+        <v>2031</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="19">
       <c r="A54" s="6">
         <v>543</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="17">
-        <v>6343</v>
-      </c>
-      <c r="F54" s="17">
-        <v>609</v>
-      </c>
-      <c r="G54" s="17">
-        <v>3283</v>
-      </c>
-      <c r="H54" s="17">
-        <v>2451</v>
-      </c>
-      <c r="I54" s="17">
-        <v>1294</v>
+      <c r="C54" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="13">
+        <v>6418</v>
+      </c>
+      <c r="F54" s="14">
+        <v>648</v>
+      </c>
+      <c r="G54" s="14">
+        <v>3331</v>
+      </c>
+      <c r="H54" s="15">
+        <v>2439</v>
+      </c>
+      <c r="I54" s="15">
+        <v>1250</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="19">
       <c r="A55" s="10">
         <v>561</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E55" s="17">
-        <v>10744</v>
-      </c>
-      <c r="F55" s="17">
-        <v>891</v>
-      </c>
-      <c r="G55" s="17">
-        <v>5243</v>
-      </c>
-      <c r="H55" s="17">
-        <v>4610</v>
-      </c>
-      <c r="I55" s="17">
-        <v>2649</v>
+      <c r="C55" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="13">
+        <v>10899</v>
+      </c>
+      <c r="F55" s="14">
+        <v>922</v>
+      </c>
+      <c r="G55" s="14">
+        <v>5313</v>
+      </c>
+      <c r="H55" s="15">
+        <v>4664</v>
+      </c>
+      <c r="I55" s="15">
+        <v>2614</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="19">
       <c r="A56" s="10">
         <v>562</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E56" s="17">
-        <v>4112</v>
-      </c>
-      <c r="F56" s="17">
-        <v>443</v>
-      </c>
-      <c r="G56" s="17">
-        <v>1955</v>
-      </c>
-      <c r="H56" s="17">
-        <v>1714</v>
-      </c>
-      <c r="I56" s="17">
-        <v>933</v>
+      <c r="C56" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="13">
+        <v>4164</v>
+      </c>
+      <c r="F56" s="14">
+        <v>446</v>
+      </c>
+      <c r="G56" s="14">
+        <v>1999</v>
+      </c>
+      <c r="H56" s="15">
+        <v>1719</v>
+      </c>
+      <c r="I56" s="15">
+        <v>915</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="19">
       <c r="A57" s="10">
         <v>563</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E57" s="17">
-        <v>3162</v>
-      </c>
-      <c r="F57" s="17">
-        <v>340</v>
-      </c>
-      <c r="G57" s="17">
-        <v>1594</v>
-      </c>
-      <c r="H57" s="17">
-        <v>1228</v>
-      </c>
-      <c r="I57" s="17">
-        <v>667</v>
+      <c r="C57" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="13">
+        <v>3169</v>
+      </c>
+      <c r="F57" s="14">
+        <v>352</v>
+      </c>
+      <c r="G57" s="14">
+        <v>1569</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1248</v>
+      </c>
+      <c r="I57" s="15">
+        <v>648</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="19">
       <c r="A58" s="6">
         <v>583</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E58" s="17">
-        <v>7406</v>
-      </c>
-      <c r="F58" s="17">
-        <v>603</v>
-      </c>
-      <c r="G58" s="17">
-        <v>3454</v>
-      </c>
-      <c r="H58" s="17">
-        <v>3349</v>
-      </c>
-      <c r="I58" s="17">
-        <v>1773</v>
+      <c r="C58" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="13">
+        <v>7514</v>
+      </c>
+      <c r="F58" s="14">
+        <v>615</v>
+      </c>
+      <c r="G58" s="14">
+        <v>3504</v>
+      </c>
+      <c r="H58" s="15">
+        <v>3395</v>
+      </c>
+      <c r="I58" s="15">
+        <v>1734</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="19">
       <c r="A59" s="6">
         <v>590</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E59" s="17">
-        <v>9884</v>
-      </c>
-      <c r="F59" s="17">
-        <v>989</v>
-      </c>
-      <c r="G59" s="17">
-        <v>4773</v>
-      </c>
-      <c r="H59" s="17">
-        <v>4122</v>
-      </c>
-      <c r="I59" s="17">
-        <v>2213</v>
+      <c r="B59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="13">
+        <v>2188</v>
+      </c>
+      <c r="F59" s="14">
+        <v>178</v>
+      </c>
+      <c r="G59" s="14">
+        <v>996</v>
+      </c>
+      <c r="H59" s="15">
+        <v>1014</v>
+      </c>
+      <c r="I59" s="15">
+        <v>599</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="19">
       <c r="A60" s="6">
         <v>588</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="17">
-        <v>2116</v>
-      </c>
-      <c r="F60" s="17">
-        <v>172</v>
-      </c>
-      <c r="G60" s="17">
-        <v>969</v>
-      </c>
-      <c r="H60" s="17">
-        <v>975</v>
-      </c>
-      <c r="I60" s="17">
-        <v>583</v>
+      <c r="B60" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="13">
+        <v>10073</v>
+      </c>
+      <c r="F60" s="14">
+        <v>1015</v>
+      </c>
+      <c r="G60" s="14">
+        <v>4905</v>
+      </c>
+      <c r="H60" s="15">
+        <v>4153</v>
+      </c>
+      <c r="I60" s="15">
+        <v>2134</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="19">
       <c r="A61" s="10">
         <v>602</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E61" s="17">
-        <v>1527</v>
-      </c>
-      <c r="F61" s="17">
-        <v>95</v>
-      </c>
-      <c r="G61" s="17">
-        <v>558</v>
-      </c>
-      <c r="H61" s="17">
-        <v>874</v>
-      </c>
-      <c r="I61" s="17">
-        <v>528</v>
+      <c r="C61" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="13">
+        <v>1571</v>
+      </c>
+      <c r="F61" s="14">
+        <v>93</v>
+      </c>
+      <c r="G61" s="14">
+        <v>588</v>
+      </c>
+      <c r="H61" s="15">
+        <v>890</v>
+      </c>
+      <c r="I61" s="15">
+        <v>536</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="19">
@@ -2416,22 +2434,22 @@
         <v>10</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E62" s="17">
-        <v>341974</v>
+        <v>345222</v>
       </c>
       <c r="F62" s="17">
-        <v>39304</v>
+        <v>40467</v>
       </c>
       <c r="G62" s="17">
-        <v>193970</v>
+        <v>196078</v>
       </c>
       <c r="H62" s="17">
-        <v>108700</v>
+        <v>108677</v>
       </c>
       <c r="I62" s="17">
-        <v>62656</v>
+        <v>60963</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="19">
@@ -2445,22 +2463,22 @@
         <v>10</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E63" s="17">
-        <v>48299</v>
+        <v>48528</v>
       </c>
       <c r="F63" s="17">
-        <v>5660</v>
+        <v>5746</v>
       </c>
       <c r="G63" s="17">
-        <v>26671</v>
+        <v>26845</v>
       </c>
       <c r="H63" s="17">
-        <v>15968</v>
+        <v>15937</v>
       </c>
       <c r="I63" s="17">
-        <v>9319</v>
+        <v>8998</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="19">
@@ -2474,22 +2492,22 @@
         <v>15</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E64" s="17">
-        <v>40334</v>
+        <v>40702</v>
       </c>
       <c r="F64" s="17">
-        <v>4578</v>
+        <v>4740</v>
       </c>
       <c r="G64" s="17">
-        <v>21899</v>
+        <v>22208</v>
       </c>
       <c r="H64" s="17">
-        <v>13857</v>
+        <v>13754</v>
       </c>
       <c r="I64" s="17">
-        <v>7629</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="19">
@@ -2503,22 +2521,22 @@
         <v>15</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E65" s="17">
-        <v>18119</v>
+        <v>18536</v>
       </c>
       <c r="F65" s="17">
-        <v>1702</v>
+        <v>1796</v>
       </c>
       <c r="G65" s="17">
-        <v>9127</v>
+        <v>9400</v>
       </c>
       <c r="H65" s="17">
-        <v>7290</v>
+        <v>7340</v>
       </c>
       <c r="I65" s="17">
-        <v>4065</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="19">
@@ -2532,22 +2550,22 @@
         <v>10</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E66" s="17">
-        <v>57300</v>
+        <v>57774</v>
       </c>
       <c r="F66" s="17">
-        <v>6612</v>
+        <v>6767</v>
       </c>
       <c r="G66" s="17">
-        <v>31156</v>
+        <v>31409</v>
       </c>
       <c r="H66" s="17">
-        <v>19532</v>
+        <v>19598</v>
       </c>
       <c r="I66" s="17">
-        <v>11562</v>
+        <v>11280</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="19">
@@ -2561,22 +2579,22 @@
         <v>10</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E67" s="17">
-        <v>13144</v>
+        <v>13344</v>
       </c>
       <c r="F67" s="17">
-        <v>1259</v>
+        <v>1317</v>
       </c>
       <c r="G67" s="17">
-        <v>6985</v>
+        <v>7099</v>
       </c>
       <c r="H67" s="17">
-        <v>4900</v>
+        <v>4928</v>
       </c>
       <c r="I67" s="17">
-        <v>2948</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="19">
@@ -2590,22 +2608,22 @@
         <v>10</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E68" s="17">
-        <v>10631</v>
+        <v>10634</v>
       </c>
       <c r="F68" s="17">
-        <v>1391</v>
+        <v>1400</v>
       </c>
       <c r="G68" s="17">
-        <v>5505</v>
+        <v>5493</v>
       </c>
       <c r="H68" s="17">
-        <v>3735</v>
+        <v>3741</v>
       </c>
       <c r="I68" s="17">
-        <v>2201</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="19">
@@ -2619,22 +2637,22 @@
         <v>10</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E69" s="17">
-        <v>6225</v>
+        <v>6343</v>
       </c>
       <c r="F69" s="17">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="G69" s="17">
-        <v>3192</v>
+        <v>3283</v>
       </c>
       <c r="H69" s="17">
-        <v>2467</v>
+        <v>2451</v>
       </c>
       <c r="I69" s="17">
-        <v>1357</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="19">
@@ -2648,22 +2666,22 @@
         <v>15</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E70" s="17">
-        <v>10607</v>
+        <v>10744</v>
       </c>
       <c r="F70" s="17">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="G70" s="17">
-        <v>5160</v>
+        <v>5243</v>
       </c>
       <c r="H70" s="17">
-        <v>4568</v>
+        <v>4610</v>
       </c>
       <c r="I70" s="17">
-        <v>2677</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="19">
@@ -2677,22 +2695,22 @@
         <v>15</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E71" s="17">
-        <v>4008</v>
+        <v>4112</v>
       </c>
       <c r="F71" s="17">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="G71" s="17">
-        <v>1884</v>
+        <v>1955</v>
       </c>
       <c r="H71" s="17">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="I71" s="17">
-        <v>960</v>
+        <v>933</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="19">
@@ -2706,22 +2724,22 @@
         <v>15</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E72" s="17">
-        <v>3186</v>
+        <v>3162</v>
       </c>
       <c r="F72" s="17">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="G72" s="17">
-        <v>1649</v>
+        <v>1594</v>
       </c>
       <c r="H72" s="17">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="I72" s="17">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="19">
@@ -2735,22 +2753,22 @@
         <v>10</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E73" s="17">
-        <v>7286</v>
+        <v>7406</v>
       </c>
       <c r="F73" s="17">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="G73" s="17">
-        <v>3395</v>
+        <v>3454</v>
       </c>
       <c r="H73" s="17">
-        <v>3311</v>
+        <v>3349</v>
       </c>
       <c r="I73" s="17">
-        <v>1825</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="19">
@@ -2764,22 +2782,22 @@
         <v>10</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E74" s="17">
-        <v>9732</v>
+        <v>9884</v>
       </c>
       <c r="F74" s="17">
-        <v>965</v>
+        <v>989</v>
       </c>
       <c r="G74" s="17">
-        <v>4663</v>
+        <v>4773</v>
       </c>
       <c r="H74" s="17">
-        <v>4104</v>
+        <v>4122</v>
       </c>
       <c r="I74" s="17">
-        <v>2279</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="19">
@@ -2793,22 +2811,22 @@
         <v>10</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E75" s="17">
-        <v>2085</v>
+        <v>2116</v>
       </c>
       <c r="F75" s="17">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G75" s="17">
-        <v>946</v>
+        <v>969</v>
       </c>
       <c r="H75" s="17">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="I75" s="17">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="19">
@@ -2822,460 +2840,896 @@
         <v>15</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E76" s="17">
-        <v>1472</v>
+        <v>1527</v>
       </c>
       <c r="F76" s="17">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G76" s="17">
+        <v>558</v>
+      </c>
+      <c r="H76" s="17">
+        <v>874</v>
+      </c>
+      <c r="I76" s="17">
         <v>528</v>
-      </c>
-      <c r="H76" s="17">
-        <v>851</v>
-      </c>
-      <c r="I76" s="17">
-        <v>513</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="19">
       <c r="A77" s="6">
         <v>201</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>35</v>
+      <c r="C77" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E77" s="17">
-        <v>339171</v>
+        <v>341974</v>
       </c>
       <c r="F77" s="17">
-        <v>38330</v>
+        <v>39304</v>
       </c>
       <c r="G77" s="17">
-        <v>192504</v>
+        <v>193970</v>
       </c>
       <c r="H77" s="17">
-        <v>108337</v>
+        <v>108700</v>
       </c>
       <c r="I77" s="17">
-        <v>63930</v>
+        <v>62656</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="19">
       <c r="A78" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>35</v>
+      <c r="C78" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E78" s="17">
-        <v>47828</v>
+        <v>48299</v>
       </c>
       <c r="F78" s="17">
-        <v>5478</v>
+        <v>5660</v>
       </c>
       <c r="G78" s="17">
-        <v>26358</v>
+        <v>26671</v>
       </c>
       <c r="H78" s="17">
-        <v>15992</v>
+        <v>15968</v>
       </c>
       <c r="I78" s="17">
-        <v>9645</v>
+        <v>9319</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="19">
       <c r="A79" s="10">
         <v>211</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D79" s="18" t="s">
-        <v>35</v>
+      <c r="D79" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E79" s="17">
-        <v>39842</v>
+        <v>40334</v>
       </c>
       <c r="F79" s="17">
-        <v>4418</v>
+        <v>4578</v>
       </c>
       <c r="G79" s="17">
-        <v>21651</v>
+        <v>21899</v>
       </c>
       <c r="H79" s="17">
-        <v>13773</v>
+        <v>13857</v>
       </c>
       <c r="I79" s="17">
-        <v>7830</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="19">
       <c r="A80" s="10">
         <v>213</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>35</v>
+      <c r="D80" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E80" s="17">
-        <v>17706</v>
+        <v>18119</v>
       </c>
       <c r="F80" s="17">
-        <v>1639</v>
+        <v>1702</v>
       </c>
       <c r="G80" s="17">
-        <v>8849</v>
+        <v>9127</v>
       </c>
       <c r="H80" s="17">
-        <v>7218</v>
+        <v>7290</v>
       </c>
       <c r="I80" s="17">
-        <v>4140</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="19">
       <c r="A81" s="6">
         <v>218</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>35</v>
+      <c r="C81" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E81" s="17">
-        <v>57008</v>
+        <v>57300</v>
       </c>
       <c r="F81" s="17">
-        <v>6488</v>
+        <v>6612</v>
       </c>
       <c r="G81" s="17">
-        <v>31032</v>
+        <v>31156</v>
       </c>
       <c r="H81" s="17">
-        <v>19488</v>
+        <v>19532</v>
       </c>
       <c r="I81" s="17">
-        <v>11812</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="19">
       <c r="A82" s="6">
         <v>521</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>35</v>
+      <c r="C82" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E82" s="17">
-        <v>12891</v>
+        <v>13144</v>
       </c>
       <c r="F82" s="17">
-        <v>1219</v>
+        <v>1259</v>
       </c>
       <c r="G82" s="17">
-        <v>6804</v>
+        <v>6985</v>
       </c>
       <c r="H82" s="17">
-        <v>4868</v>
+        <v>4900</v>
       </c>
       <c r="I82" s="17">
-        <v>3007</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="19">
       <c r="A83" s="6">
         <v>541</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>35</v>
+      <c r="C83" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E83" s="17">
-        <v>10555</v>
+        <v>10631</v>
       </c>
       <c r="F83" s="17">
-        <v>1360</v>
+        <v>1391</v>
       </c>
       <c r="G83" s="17">
-        <v>5455</v>
+        <v>5505</v>
       </c>
       <c r="H83" s="17">
-        <v>3740</v>
+        <v>3735</v>
       </c>
       <c r="I83" s="17">
-        <v>2310</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="19">
       <c r="A84" s="6">
         <v>543</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B84" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>35</v>
+      <c r="C84" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E84" s="17">
-        <v>6125</v>
+        <v>6225</v>
       </c>
       <c r="F84" s="17">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="G84" s="17">
-        <v>3128</v>
+        <v>3192</v>
       </c>
       <c r="H84" s="17">
-        <v>2448</v>
+        <v>2467</v>
       </c>
       <c r="I84" s="17">
-        <v>1398</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="19">
       <c r="A85" s="10">
         <v>561</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C85" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>35</v>
+      <c r="C85" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E85" s="17">
-        <v>10500</v>
+        <v>10607</v>
       </c>
       <c r="F85" s="17">
-        <v>842</v>
+        <v>879</v>
       </c>
       <c r="G85" s="17">
-        <v>5116</v>
+        <v>5160</v>
       </c>
       <c r="H85" s="17">
-        <v>4542</v>
+        <v>4568</v>
       </c>
       <c r="I85" s="17">
-        <v>2725</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="19">
       <c r="A86" s="10">
         <v>562</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C86" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>35</v>
+      <c r="C86" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E86" s="17">
-        <v>3910</v>
+        <v>4008</v>
       </c>
       <c r="F86" s="17">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G86" s="17">
-        <v>1817</v>
+        <v>1884</v>
       </c>
       <c r="H86" s="17">
-        <v>1694</v>
+        <v>1705</v>
       </c>
       <c r="I86" s="17">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="19">
       <c r="A87" s="10">
         <v>563</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>35</v>
+      <c r="C87" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E87" s="17">
-        <v>3216</v>
+        <v>3186</v>
       </c>
       <c r="F87" s="17">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G87" s="17">
-        <v>1700</v>
+        <v>1649</v>
       </c>
       <c r="H87" s="17">
-        <v>1205</v>
+        <v>1223</v>
       </c>
       <c r="I87" s="17">
-        <v>690</v>
+        <v>671</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="19">
       <c r="A88" s="6">
         <v>583</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>35</v>
+      <c r="C88" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E88" s="17">
-        <v>7104</v>
+        <v>7286</v>
       </c>
       <c r="F88" s="17">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="G88" s="17">
-        <v>3309</v>
+        <v>3395</v>
       </c>
       <c r="H88" s="17">
-        <v>3255</v>
+        <v>3311</v>
       </c>
       <c r="I88" s="17">
-        <v>1859</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="19">
       <c r="A89" s="6">
         <v>590</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C89" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>35</v>
+      <c r="C89" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E89" s="17">
-        <v>9634</v>
+        <v>9732</v>
       </c>
       <c r="F89" s="17">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="G89" s="17">
-        <v>4590</v>
+        <v>4663</v>
       </c>
       <c r="H89" s="17">
-        <v>4090</v>
+        <v>4104</v>
       </c>
       <c r="I89" s="17">
-        <v>2335</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="19">
       <c r="A90" s="6">
         <v>588</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>35</v>
+      <c r="C90" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E90" s="17">
-        <v>2031</v>
+        <v>2085</v>
       </c>
       <c r="F90" s="17">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G90" s="17">
-        <v>913</v>
+        <v>946</v>
       </c>
       <c r="H90" s="17">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="I90" s="17">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="19">
       <c r="A91" s="10">
         <v>602</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="18" t="s">
+      <c r="C91" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91" s="17">
+        <v>1472</v>
+      </c>
+      <c r="F91" s="17">
+        <v>93</v>
+      </c>
+      <c r="G91" s="17">
+        <v>528</v>
+      </c>
+      <c r="H91" s="17">
+        <v>851</v>
+      </c>
+      <c r="I91" s="17">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="19">
+      <c r="A92" s="6">
+        <v>201</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E91" s="17">
+      <c r="E92" s="17">
+        <v>339171</v>
+      </c>
+      <c r="F92" s="17">
+        <v>38330</v>
+      </c>
+      <c r="G92" s="17">
+        <v>192504</v>
+      </c>
+      <c r="H92" s="17">
+        <v>108337</v>
+      </c>
+      <c r="I92" s="17">
+        <v>63930</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="19">
+      <c r="A93" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="17">
+        <v>47828</v>
+      </c>
+      <c r="F93" s="17">
+        <v>5478</v>
+      </c>
+      <c r="G93" s="17">
+        <v>26358</v>
+      </c>
+      <c r="H93" s="17">
+        <v>15992</v>
+      </c>
+      <c r="I93" s="17">
+        <v>9645</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="19">
+      <c r="A94" s="10">
+        <v>211</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="17">
+        <v>39842</v>
+      </c>
+      <c r="F94" s="17">
+        <v>4418</v>
+      </c>
+      <c r="G94" s="17">
+        <v>21651</v>
+      </c>
+      <c r="H94" s="17">
+        <v>13773</v>
+      </c>
+      <c r="I94" s="17">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="19">
+      <c r="A95" s="10">
+        <v>213</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="17">
+        <v>17706</v>
+      </c>
+      <c r="F95" s="17">
+        <v>1639</v>
+      </c>
+      <c r="G95" s="17">
+        <v>8849</v>
+      </c>
+      <c r="H95" s="17">
+        <v>7218</v>
+      </c>
+      <c r="I95" s="17">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="19">
+      <c r="A96" s="6">
+        <v>218</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="17">
+        <v>57008</v>
+      </c>
+      <c r="F96" s="17">
+        <v>6488</v>
+      </c>
+      <c r="G96" s="17">
+        <v>31032</v>
+      </c>
+      <c r="H96" s="17">
+        <v>19488</v>
+      </c>
+      <c r="I96" s="17">
+        <v>11812</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="19">
+      <c r="A97" s="6">
+        <v>521</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="17">
+        <v>12891</v>
+      </c>
+      <c r="F97" s="17">
+        <v>1219</v>
+      </c>
+      <c r="G97" s="17">
+        <v>6804</v>
+      </c>
+      <c r="H97" s="17">
+        <v>4868</v>
+      </c>
+      <c r="I97" s="17">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="19">
+      <c r="A98" s="6">
+        <v>541</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="17">
+        <v>10555</v>
+      </c>
+      <c r="F98" s="17">
+        <v>1360</v>
+      </c>
+      <c r="G98" s="17">
+        <v>5455</v>
+      </c>
+      <c r="H98" s="17">
+        <v>3740</v>
+      </c>
+      <c r="I98" s="17">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="19">
+      <c r="A99" s="6">
+        <v>543</v>
+      </c>
+      <c r="B99" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="17">
+        <v>6125</v>
+      </c>
+      <c r="F99" s="17">
+        <v>549</v>
+      </c>
+      <c r="G99" s="17">
+        <v>3128</v>
+      </c>
+      <c r="H99" s="17">
+        <v>2448</v>
+      </c>
+      <c r="I99" s="17">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="19">
+      <c r="A100" s="10">
+        <v>561</v>
+      </c>
+      <c r="B100" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="17">
+        <v>10500</v>
+      </c>
+      <c r="F100" s="17">
+        <v>842</v>
+      </c>
+      <c r="G100" s="17">
+        <v>5116</v>
+      </c>
+      <c r="H100" s="17">
+        <v>4542</v>
+      </c>
+      <c r="I100" s="17">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="19">
+      <c r="A101" s="10">
+        <v>562</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="17">
+        <v>3910</v>
+      </c>
+      <c r="F101" s="17">
+        <v>399</v>
+      </c>
+      <c r="G101" s="17">
+        <v>1817</v>
+      </c>
+      <c r="H101" s="17">
+        <v>1694</v>
+      </c>
+      <c r="I101" s="17">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="19">
+      <c r="A102" s="10">
+        <v>563</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="17">
+        <v>3216</v>
+      </c>
+      <c r="F102" s="17">
+        <v>311</v>
+      </c>
+      <c r="G102" s="17">
+        <v>1700</v>
+      </c>
+      <c r="H102" s="17">
+        <v>1205</v>
+      </c>
+      <c r="I102" s="17">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="19">
+      <c r="A103" s="6">
+        <v>583</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="17">
+        <v>7104</v>
+      </c>
+      <c r="F103" s="17">
+        <v>540</v>
+      </c>
+      <c r="G103" s="17">
+        <v>3309</v>
+      </c>
+      <c r="H103" s="17">
+        <v>3255</v>
+      </c>
+      <c r="I103" s="17">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="19">
+      <c r="A104" s="6">
+        <v>590</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="17">
+        <v>9634</v>
+      </c>
+      <c r="F104" s="17">
+        <v>954</v>
+      </c>
+      <c r="G104" s="17">
+        <v>4590</v>
+      </c>
+      <c r="H104" s="17">
+        <v>4090</v>
+      </c>
+      <c r="I104" s="17">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="19">
+      <c r="A105" s="6">
+        <v>588</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="17">
+        <v>2031</v>
+      </c>
+      <c r="F105" s="17">
+        <v>164</v>
+      </c>
+      <c r="G105" s="17">
+        <v>913</v>
+      </c>
+      <c r="H105" s="17">
+        <v>954</v>
+      </c>
+      <c r="I105" s="17">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="19">
+      <c r="A106" s="10">
+        <v>602</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="17">
         <v>1438</v>
       </c>
-      <c r="F91" s="17">
+      <c r="F106" s="17">
         <v>97</v>
       </c>
-      <c r="G91" s="17">
+      <c r="G106" s="17">
         <v>521</v>
       </c>
-      <c r="H91" s="17">
+      <c r="H106" s="17">
         <v>820</v>
       </c>
-      <c r="I91" s="17">
+      <c r="I106" s="17">
         <v>516</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>